--- a/artfynd/A 24851-2025 artfynd.xlsx
+++ b/artfynd/A 24851-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,68 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>77943519</v>
+        <v>118036261</v>
       </c>
       <c r="B2" t="n">
-        <v>42541</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101248</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violett guldvinge</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycaena helle</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nedre Harrsjövägskälet, Jmt</t>
+          <t>Harrån_Slammeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531609.0662193769</v>
+        <v>531886</v>
       </c>
       <c r="R2" t="n">
-        <v>6947946.64422737</v>
+        <v>6947843</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-05-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-05-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,6 +769,1004 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>86374134</v>
+      </c>
+      <c r="B3" t="n">
+        <v>41670</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100453</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Trolldruvemätare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Baptria tibiale</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Esper, 1790)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>slammeråsen himlastigen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>531743</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6948065</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-06-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-06-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>77943519</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43249</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>101248</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Violett guldvinge</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycaena helle</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nedre Harrsjövägskälet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>531609</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6947947</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-05-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-05-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>66777525</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nedre Harrsjövägskälet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>531609</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6947947</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-07-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>87638397</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storharrsjövägen intill E14, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>531610</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6947932</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-08-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-08-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Skogsväg</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kerstin Frostberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kerstin Frostberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118036260</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Harrån_slammeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>531584</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6947941</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7061349</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>slammeråsen himlastigen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>531723</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6948075</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2013-10-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2013-10-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ca 10 plantor i vägkant himlastigen, fäll 10 träd</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7061350</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>slammeråsen himlastigen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>531743</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6948065</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2013-10-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2013-10-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bärande med gnagspår</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118035696</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Himlastigen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>531728</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6948062</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118036264</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Harrån_Slammeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>531730</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6948071</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
